--- a/research/iterations/a03e-guard/qualified-results.xlsx
+++ b/research/iterations/a03e-guard/qualified-results.xlsx
@@ -1722,10 +1722,10 @@
         <v>1</v>
       </c>
       <c r="T2">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="U2">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="V2">
         <v>50</v>
@@ -1787,13 +1787,13 @@
         <v>0.6</v>
       </c>
       <c r="S3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T3">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="U3">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="V3">
         <v>50</v>
